--- a/VALIDATION/LuoDDQN_tight_duedate_JA_only_1to10.xlsx
+++ b/VALIDATION/LuoDDQN_tight_duedate_JA_only_1to10.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7315</v>
+        <v>68325</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9955</v>
+        <v>77435</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9965</v>
+        <v>66050</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3985</v>
+        <v>68005</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3700</v>
+        <v>64285</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3320</v>
+        <v>62675</v>
       </c>
     </row>
     <row r="8">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3705</v>
+        <v>66115</v>
       </c>
     </row>
     <row r="9">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4485</v>
+        <v>64705</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4580</v>
+        <v>67320</v>
       </c>
     </row>
     <row r="11">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4640</v>
+        <v>64895</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3615</v>
+        <v>66365</v>
       </c>
     </row>
     <row r="13">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1840</v>
+        <v>66070</v>
       </c>
     </row>
     <row r="14">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11045</v>
+        <v>78620</v>
       </c>
     </row>
     <row r="15">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9655</v>
+        <v>78745</v>
       </c>
     </row>
     <row r="16">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10390</v>
+        <v>67415</v>
       </c>
     </row>
     <row r="17">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>19045</v>
+        <v>80790</v>
       </c>
     </row>
     <row r="18">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>16030</v>
+        <v>86180</v>
       </c>
     </row>
     <row r="19">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>16975</v>
+        <v>87210</v>
       </c>
     </row>
     <row r="20">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>935</v>
+        <v>68435</v>
       </c>
     </row>
     <row r="21">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1690</v>
+        <v>63280</v>
       </c>
     </row>
     <row r="22">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1740</v>
+        <v>64950</v>
       </c>
     </row>
     <row r="23">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12515</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="24">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>20460</v>
+        <v>83565</v>
       </c>
     </row>
     <row r="25">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>20245</v>
+        <v>76235</v>
       </c>
     </row>
     <row r="26">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1785</v>
+        <v>63665</v>
       </c>
     </row>
     <row r="27">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2770</v>
+        <v>65650</v>
       </c>
     </row>
     <row r="28">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2120</v>
+        <v>65100</v>
       </c>
     </row>
     <row r="29">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4565</v>
+        <v>75700</v>
       </c>
     </row>
     <row r="30">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9595</v>
+        <v>75265</v>
       </c>
     </row>
     <row r="31">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7085</v>
+        <v>64145</v>
       </c>
     </row>
   </sheetData>
